--- a/Layout Integração - Reforma Tributária/Layout NFCom Reforma Tributária.xlsx
+++ b/Layout Integração - Reforma Tributária/Layout NFCom Reforma Tributária.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="jM7jW9EWBahqqallf6bBOmto/LOAV0LsltEfyD+QVf4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Kbj5cyuQrwT8jMFY/GSkUNt3O9Ff7HCzAHgG9cOFUUU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3427" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3433" uniqueCount="1068">
   <si>
     <t>Layout XML NFCOM 1.00</t>
   </si>
@@ -3114,19 +3114,43 @@
     <t>Autorizados para download do XML do DF-e</t>
   </si>
   <si>
-    <t>0-10</t>
-  </si>
-  <si>
     <t>Informar CNPJ ou CPF. Preencher os zeros não significativos.</t>
   </si>
   <si>
     <t>S02</t>
   </si>
   <si>
+    <t>autXMLItem</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t xml:space="preserve">Não informar este grupo quando a integração for API REST
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="11.0"/>
+      </rPr>
+      <t>Cada grupo informado deve conter apenas 1 CNPJ ou CPF informado</t>
+    </r>
+  </si>
+  <si>
+    <t>S03</t>
+  </si>
+  <si>
     <t>CNPJ do autorizado</t>
   </si>
   <si>
-    <t>S03</t>
+    <t>S04</t>
   </si>
   <si>
     <t>CPF do autorizado</t>
@@ -3292,8 +3316,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="d\-m"/>
+    <numFmt numFmtId="165" formatCode="d-m"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -3469,7 +3494,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="78">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3660,6 +3685,24 @@
     <xf borderId="4" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3668,6 +3711,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3882,11 +3928,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
     <col customWidth="1" min="2" max="2" width="13.13"/>
     <col customWidth="1" min="3" max="3" width="26.88"/>
     <col customWidth="1" min="4" max="4" width="53.5"/>
-    <col customWidth="1" min="5" max="6" width="12.63"/>
     <col customWidth="1" min="9" max="9" width="8.5"/>
     <col customWidth="1" min="10" max="10" width="60.25"/>
     <col customWidth="1" hidden="1" min="11" max="11" width="26.13"/>
@@ -17848,67 +17892,59 @@
         <v>13</v>
       </c>
       <c r="G434" s="13"/>
-      <c r="H434" s="13" t="s">
-        <v>1008</v>
+      <c r="H434" s="68" t="s">
+        <v>110</v>
       </c>
       <c r="I434" s="13" t="s">
         <v>111</v>
       </c>
       <c r="J434" s="17" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="K434" s="11" t="s">
         <v>21</v>
       </c>
       <c r="L434" s="62"/>
     </row>
-    <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="13">
-        <f t="shared" ref="A435:A436" si="37">A434+1</f>
-        <v>315</v>
-      </c>
-      <c r="B435" s="13" t="s">
+    <row r="435">
+      <c r="A435" s="69">
+        <v>315.0</v>
+      </c>
+      <c r="B435" s="69" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C435" s="69" t="s">
         <v>1010</v>
       </c>
-      <c r="C435" s="13" t="s">
+      <c r="D435" s="70"/>
+      <c r="E435" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F435" s="69" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G435" s="27"/>
+      <c r="H435" s="71">
+        <v>46296.0</v>
+      </c>
+      <c r="I435" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="J435" s="72" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K435" s="11"/>
+      <c r="L435" s="62"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="68">
+        <v>316.0</v>
+      </c>
+      <c r="B436" s="68" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C436" s="13" t="s">
         <v>155</v>
-      </c>
-      <c r="D435" s="14" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E435" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F435" s="13" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G435" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="H435" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I435" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J435" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="K435" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="L435" s="62"/>
-    </row>
-    <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="13">
-        <f t="shared" si="37"/>
-        <v>316</v>
-      </c>
-      <c r="B436" s="13" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C436" s="13" t="s">
-        <v>231</v>
       </c>
       <c r="D436" s="14" t="s">
         <v>1013</v>
@@ -17916,396 +17952,398 @@
       <c r="E436" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="F436" s="13" t="s">
-        <v>1005</v>
+      <c r="F436" s="68" t="s">
+        <v>1009</v>
       </c>
       <c r="G436" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H436" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I436" s="16" t="s">
-        <v>20</v>
+        <v>157</v>
+      </c>
+      <c r="H436" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="I436" s="68" t="s">
+        <v>111</v>
       </c>
       <c r="J436" s="17" t="s">
         <v>158</v>
       </c>
       <c r="K436" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="L436" s="62"/>
+    </row>
+    <row r="437" ht="12.75" customHeight="1">
+      <c r="A437" s="13">
+        <f>A436+1</f>
+        <v>317</v>
+      </c>
+      <c r="B437" s="68" t="s">
         <v>1014</v>
       </c>
-      <c r="L436" s="62"/>
-    </row>
-    <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="18"/>
-      <c r="B437" s="2"/>
-      <c r="C437" s="2"/>
-      <c r="D437" s="2"/>
-      <c r="E437" s="2"/>
-      <c r="F437" s="2"/>
-      <c r="G437" s="2"/>
-      <c r="H437" s="2"/>
-      <c r="I437" s="2"/>
-      <c r="J437" s="3"/>
-      <c r="K437" s="17"/>
+      <c r="C437" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D437" s="14" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E437" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F437" s="68" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G437" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="H437" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="I437" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="J437" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="K437" s="17" t="s">
+        <v>1016</v>
+      </c>
       <c r="L437" s="62"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B438" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C438" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D438" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E438" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F438" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G438" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H438" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I438" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J438" s="11" t="s">
-        <v>10</v>
-      </c>
+      <c r="A438" s="18"/>
+      <c r="B438" s="2"/>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
+      <c r="E438" s="2"/>
+      <c r="F438" s="2"/>
+      <c r="G438" s="2"/>
+      <c r="H438" s="2"/>
+      <c r="I438" s="2"/>
+      <c r="J438" s="3"/>
       <c r="K438" s="17"/>
       <c r="L438" s="62"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="37" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B439" s="2"/>
-      <c r="C439" s="2"/>
-      <c r="D439" s="2"/>
-      <c r="E439" s="2"/>
-      <c r="F439" s="2"/>
-      <c r="G439" s="2"/>
-      <c r="H439" s="2"/>
-      <c r="I439" s="2"/>
-      <c r="J439" s="2"/>
-      <c r="K439" s="3"/>
+      <c r="A439" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B439" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C439" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D439" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E439" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F439" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G439" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H439" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I439" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J439" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K439" s="17"/>
       <c r="L439" s="62"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="13">
-        <f>A436+1</f>
-        <v>317</v>
-      </c>
-      <c r="B440" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C440" s="13" t="s">
+      <c r="A440" s="37" t="s">
         <v>1017</v>
       </c>
-      <c r="D440" s="14" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E440" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F440" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G440" s="13"/>
-      <c r="H440" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I440" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="J440" s="14"/>
-      <c r="K440" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="B440" s="2"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
+      <c r="E440" s="2"/>
+      <c r="F440" s="2"/>
+      <c r="G440" s="2"/>
+      <c r="H440" s="2"/>
+      <c r="I440" s="2"/>
+      <c r="J440" s="2"/>
+      <c r="K440" s="3"/>
       <c r="L440" s="62"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="13">
-        <f t="shared" ref="A441:A442" si="38">A440+1</f>
+        <f>A437+1</f>
         <v>318</v>
       </c>
       <c r="B441" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C441" s="13" t="s">
         <v>1019</v>
       </c>
-      <c r="C441" s="13" t="s">
+      <c r="D441" s="14" t="s">
         <v>1020</v>
       </c>
-      <c r="D441" s="14" t="s">
-        <v>1021</v>
-      </c>
       <c r="E441" s="13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F441" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G441" s="13" t="s">
-        <v>1022</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="G441" s="13"/>
       <c r="H441" s="13" t="s">
         <v>110</v>
       </c>
       <c r="I441" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J441" s="17" t="s">
-        <v>1023</v>
-      </c>
-      <c r="K441" s="17" t="s">
-        <v>995</v>
+      <c r="J441" s="14"/>
+      <c r="K441" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="L441" s="62"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="13">
-        <f t="shared" si="38"/>
+        <f t="shared" ref="A442:A443" si="37">A441+1</f>
         <v>319</v>
       </c>
       <c r="B442" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C442" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D442" s="14" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E442" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F442" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G442" s="13" t="s">
         <v>1024</v>
       </c>
-      <c r="C442" s="13" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D442" s="14" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E442" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F442" s="13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G442" s="13" t="s">
-        <v>1027</v>
-      </c>
       <c r="H442" s="13" t="s">
-        <v>1028</v>
+        <v>110</v>
       </c>
       <c r="I442" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J442" s="17"/>
+      <c r="J442" s="17" t="s">
+        <v>1025</v>
+      </c>
       <c r="K442" s="17" t="s">
+        <v>995</v>
+      </c>
+      <c r="L442" s="62"/>
+    </row>
+    <row r="443" ht="12.75" customHeight="1">
+      <c r="A443" s="13">
+        <f t="shared" si="37"/>
+        <v>320</v>
+      </c>
+      <c r="B443" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C443" s="13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D443" s="14" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E443" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F443" s="13" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G443" s="13" t="s">
         <v>1029</v>
       </c>
-      <c r="L442" s="62"/>
-    </row>
-    <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="18"/>
-      <c r="B443" s="2"/>
-      <c r="C443" s="2"/>
-      <c r="D443" s="2"/>
-      <c r="E443" s="2"/>
-      <c r="F443" s="2"/>
-      <c r="G443" s="2"/>
-      <c r="H443" s="2"/>
-      <c r="I443" s="2"/>
-      <c r="J443" s="3"/>
-      <c r="K443" s="17"/>
+      <c r="H443" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I443" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J443" s="17"/>
+      <c r="K443" s="17" t="s">
+        <v>1031</v>
+      </c>
       <c r="L443" s="62"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B444" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C444" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D444" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E444" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F444" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G444" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H444" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I444" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J444" s="11" t="s">
-        <v>10</v>
-      </c>
+      <c r="A444" s="18"/>
+      <c r="B444" s="2"/>
+      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
+      <c r="E444" s="2"/>
+      <c r="F444" s="2"/>
+      <c r="G444" s="2"/>
+      <c r="H444" s="2"/>
+      <c r="I444" s="2"/>
+      <c r="J444" s="3"/>
       <c r="K444" s="17"/>
       <c r="L444" s="62"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="37" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B445" s="2"/>
-      <c r="C445" s="2"/>
-      <c r="D445" s="2"/>
-      <c r="E445" s="2"/>
-      <c r="F445" s="2"/>
-      <c r="G445" s="2"/>
-      <c r="H445" s="2"/>
-      <c r="I445" s="2"/>
-      <c r="J445" s="2"/>
-      <c r="K445" s="3"/>
+      <c r="A445" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B445" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C445" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D445" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E445" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F445" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G445" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H445" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I445" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J445" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K445" s="17"/>
       <c r="L445" s="62"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="13">
-        <f>A442+1</f>
-        <v>320</v>
-      </c>
-      <c r="B446" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C446" s="13" t="s">
+      <c r="A446" s="37" t="s">
         <v>1032</v>
       </c>
-      <c r="D446" s="14" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E446" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F446" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G446" s="13"/>
-      <c r="H446" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I446" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="J446" s="14"/>
-      <c r="K446" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="B446" s="2"/>
+      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
+      <c r="E446" s="2"/>
+      <c r="F446" s="2"/>
+      <c r="G446" s="2"/>
+      <c r="H446" s="2"/>
+      <c r="I446" s="2"/>
+      <c r="J446" s="2"/>
+      <c r="K446" s="3"/>
       <c r="L446" s="62"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="13">
-        <f t="shared" ref="A447:A452" si="39">A446+1</f>
+        <f>A443+1</f>
         <v>321</v>
       </c>
       <c r="B447" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C447" s="13" t="s">
         <v>1034</v>
-      </c>
-      <c r="C447" s="13" t="s">
-        <v>155</v>
       </c>
       <c r="D447" s="14" t="s">
         <v>1035</v>
       </c>
       <c r="E447" s="13" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F447" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G447" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="H447" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I447" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J447" s="17" t="s">
-        <v>1036</v>
-      </c>
-      <c r="K447" s="17" t="s">
-        <v>166</v>
+        <v>13</v>
+      </c>
+      <c r="G447" s="13"/>
+      <c r="H447" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I447" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J447" s="14"/>
+      <c r="K447" s="11" t="s">
+        <v>21</v>
       </c>
       <c r="L447" s="62"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="A448:A453" si="38">A447+1</f>
         <v>322</v>
       </c>
       <c r="B448" s="13" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C448" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D448" s="14" t="s">
         <v>1037</v>
       </c>
-      <c r="C448" s="13" t="s">
+      <c r="E448" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F448" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G448" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="H448" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I448" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J448" s="17" t="s">
         <v>1038</v>
       </c>
-      <c r="D448" s="14" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E448" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F448" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G448" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H448" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I448" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J448" s="17" t="s">
-        <v>1040</v>
-      </c>
       <c r="K448" s="17" t="s">
-        <v>808</v>
+        <v>166</v>
       </c>
       <c r="L448" s="62"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>323</v>
       </c>
       <c r="B449" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C449" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D449" s="14" t="s">
         <v>1041</v>
       </c>
-      <c r="C449" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D449" s="14" t="s">
+      <c r="E449" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F449" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G449" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H449" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I449" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J449" s="17" t="s">
         <v>1042</v>
       </c>
-      <c r="E449" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F449" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G449" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="H449" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I449" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J449" s="17"/>
       <c r="K449" s="17" t="s">
         <v>808</v>
       </c>
@@ -18313,14 +18351,14 @@
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>324</v>
       </c>
       <c r="B450" s="13" t="s">
         <v>1043</v>
       </c>
       <c r="C450" s="13" t="s">
-        <v>211</v>
+        <v>270</v>
       </c>
       <c r="D450" s="14" t="s">
         <v>1044</v>
@@ -18329,10 +18367,10 @@
         <v>25</v>
       </c>
       <c r="F450" s="13" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G450" s="13" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="H450" s="15" t="s">
         <v>19</v>
@@ -18340,936 +18378,962 @@
       <c r="I450" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="J450" s="17" t="s">
-        <v>1045</v>
-      </c>
+      <c r="J450" s="17"/>
       <c r="K450" s="17" t="s">
-        <v>322</v>
+        <v>808</v>
       </c>
       <c r="L450" s="62"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>325</v>
       </c>
       <c r="B451" s="13" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C451" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D451" s="14" t="s">
         <v>1046</v>
       </c>
-      <c r="C451" s="13" t="s">
+      <c r="E451" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F451" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G451" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="H451" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I451" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J451" s="17" t="s">
         <v>1047</v>
       </c>
-      <c r="D451" s="14" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E451" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="F451" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G451" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="H451" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I451" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J451" s="17" t="s">
-        <v>1049</v>
-      </c>
       <c r="K451" s="17" t="s">
-        <v>1050</v>
+        <v>322</v>
       </c>
       <c r="L451" s="62"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="13">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>326</v>
       </c>
       <c r="B452" s="13" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C452" s="13" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="D452" s="14" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E452" s="13" t="s">
         <v>116</v>
       </c>
       <c r="F452" s="13" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G452" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="H452" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I452" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J452" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K452" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L452" s="62"/>
+    </row>
+    <row r="453" ht="12.75" customHeight="1">
+      <c r="A453" s="13">
+        <f t="shared" si="38"/>
+        <v>327</v>
+      </c>
+      <c r="B453" s="13" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C453" s="13" t="s">
         <v>1054</v>
       </c>
-      <c r="H452" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I452" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J452" s="17" t="s">
+      <c r="D453" s="14" t="s">
         <v>1055</v>
       </c>
-      <c r="K452" s="17" t="s">
+      <c r="E453" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="F453" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G453" s="13" t="s">
         <v>1056</v>
       </c>
-      <c r="L452" s="62"/>
-    </row>
-    <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="18"/>
-      <c r="B453" s="2"/>
-      <c r="C453" s="2"/>
-      <c r="D453" s="2"/>
-      <c r="E453" s="2"/>
-      <c r="F453" s="2"/>
-      <c r="G453" s="2"/>
-      <c r="H453" s="2"/>
-      <c r="I453" s="2"/>
-      <c r="J453" s="3"/>
-      <c r="K453" s="17"/>
+      <c r="H453" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I453" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J453" s="17" t="s">
+        <v>1057</v>
+      </c>
+      <c r="K453" s="17" t="s">
+        <v>1058</v>
+      </c>
       <c r="L453" s="62"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B454" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C454" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D454" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E454" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F454" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G454" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="H454" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="I454" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J454" s="11" t="s">
-        <v>10</v>
-      </c>
+      <c r="A454" s="18"/>
+      <c r="B454" s="2"/>
+      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
+      <c r="E454" s="2"/>
+      <c r="F454" s="2"/>
+      <c r="G454" s="2"/>
+      <c r="H454" s="2"/>
+      <c r="I454" s="2"/>
+      <c r="J454" s="3"/>
       <c r="K454" s="17"/>
       <c r="L454" s="62"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="37" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B455" s="2"/>
-      <c r="C455" s="2"/>
-      <c r="D455" s="2"/>
-      <c r="E455" s="2"/>
-      <c r="F455" s="2"/>
-      <c r="G455" s="2"/>
-      <c r="H455" s="2"/>
-      <c r="I455" s="2"/>
-      <c r="J455" s="2"/>
-      <c r="K455" s="3"/>
+      <c r="A455" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B455" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C455" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D455" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E455" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F455" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G455" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H455" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I455" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J455" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K455" s="17"/>
       <c r="L455" s="62"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="13">
-        <f>A452+1</f>
-        <v>327</v>
-      </c>
-      <c r="B456" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C456" s="13" t="s">
+      <c r="A456" s="37" t="s">
         <v>1059</v>
       </c>
-      <c r="D456" s="13" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E456" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F456" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G456" s="13"/>
-      <c r="H456" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I456" s="13"/>
-      <c r="J456" s="13"/>
-      <c r="K456" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="B456" s="2"/>
+      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
+      <c r="E456" s="2"/>
+      <c r="F456" s="2"/>
+      <c r="G456" s="2"/>
+      <c r="H456" s="2"/>
+      <c r="I456" s="2"/>
+      <c r="J456" s="2"/>
+      <c r="K456" s="3"/>
       <c r="L456" s="62"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="13">
-        <f>A456+1</f>
+        <f>A453+1</f>
         <v>328</v>
       </c>
       <c r="B457" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C457" s="13" t="s">
         <v>1061</v>
       </c>
-      <c r="C457" s="13" t="s">
+      <c r="D457" s="13" t="s">
         <v>1062</v>
       </c>
-      <c r="D457" s="14" t="s">
+      <c r="E457" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F457" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G457" s="13"/>
+      <c r="H457" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I457" s="13"/>
+      <c r="J457" s="13"/>
+      <c r="K457" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L457" s="62"/>
+    </row>
+    <row r="458" ht="12.75" customHeight="1">
+      <c r="A458" s="13">
+        <f>A457+1</f>
+        <v>329</v>
+      </c>
+      <c r="B458" s="13" t="s">
         <v>1063</v>
       </c>
-      <c r="E457" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F457" s="13" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G457" s="13" t="s">
+      <c r="C458" s="13" t="s">
         <v>1064</v>
       </c>
-      <c r="H457" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I457" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="J457" s="17"/>
-      <c r="K457" s="17" t="s">
+      <c r="D458" s="14" t="s">
         <v>1065</v>
       </c>
-      <c r="L457" s="62"/>
-    </row>
-    <row r="458" ht="12.75" customHeight="1">
-      <c r="B458" s="6"/>
-      <c r="C458" s="68"/>
-      <c r="D458" s="69"/>
-      <c r="I458" s="6"/>
-      <c r="J458" s="70"/>
-      <c r="K458" s="69"/>
+      <c r="E458" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F458" s="13" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G458" s="13" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H458" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="I458" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="J458" s="17"/>
+      <c r="K458" s="17" t="s">
+        <v>1067</v>
+      </c>
       <c r="L458" s="62"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="B459" s="6"/>
-      <c r="C459" s="68"/>
-      <c r="D459" s="69"/>
+      <c r="C459" s="74"/>
+      <c r="D459" s="75"/>
       <c r="I459" s="6"/>
-      <c r="J459" s="70"/>
-      <c r="K459" s="69"/>
+      <c r="J459" s="76"/>
+      <c r="K459" s="75"/>
       <c r="L459" s="62"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="B460" s="6"/>
-      <c r="C460" s="68"/>
-      <c r="D460" s="69"/>
+      <c r="C460" s="74"/>
+      <c r="D460" s="75"/>
       <c r="I460" s="6"/>
-      <c r="J460" s="70"/>
-      <c r="K460" s="69"/>
+      <c r="J460" s="76"/>
+      <c r="K460" s="75"/>
       <c r="L460" s="62"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="B461" s="6"/>
-      <c r="C461" s="68"/>
-      <c r="D461" s="69"/>
+      <c r="C461" s="77"/>
+      <c r="D461" s="75"/>
       <c r="I461" s="6"/>
-      <c r="J461" s="70"/>
-      <c r="K461" s="69"/>
+      <c r="J461" s="76"/>
+      <c r="K461" s="75"/>
       <c r="L461" s="62"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="B462" s="6"/>
-      <c r="C462" s="68"/>
-      <c r="D462" s="69"/>
+      <c r="C462" s="74"/>
+      <c r="D462" s="75"/>
       <c r="I462" s="6"/>
-      <c r="J462" s="70"/>
-      <c r="K462" s="69"/>
+      <c r="J462" s="76"/>
+      <c r="K462" s="75"/>
       <c r="L462" s="62"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="B463" s="6"/>
-      <c r="C463" s="68"/>
-      <c r="D463" s="69"/>
+      <c r="C463" s="74"/>
+      <c r="D463" s="75"/>
       <c r="I463" s="6"/>
-      <c r="J463" s="70"/>
-      <c r="K463" s="69"/>
+      <c r="J463" s="76"/>
+      <c r="K463" s="75"/>
       <c r="L463" s="62"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="B464" s="6"/>
-      <c r="C464" s="68"/>
-      <c r="D464" s="69"/>
+      <c r="C464" s="74"/>
+      <c r="D464" s="75"/>
       <c r="I464" s="6"/>
-      <c r="J464" s="70"/>
-      <c r="K464" s="69"/>
+      <c r="J464" s="76"/>
+      <c r="K464" s="75"/>
       <c r="L464" s="62"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="B465" s="6"/>
-      <c r="C465" s="68"/>
-      <c r="D465" s="69"/>
+      <c r="C465" s="74"/>
+      <c r="D465" s="75"/>
       <c r="I465" s="6"/>
-      <c r="J465" s="70"/>
-      <c r="K465" s="69"/>
+      <c r="J465" s="76"/>
+      <c r="K465" s="75"/>
       <c r="L465" s="62"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="B466" s="6"/>
-      <c r="C466" s="68"/>
-      <c r="D466" s="69"/>
+      <c r="C466" s="74"/>
+      <c r="D466" s="75"/>
       <c r="I466" s="6"/>
-      <c r="J466" s="70"/>
-      <c r="K466" s="69"/>
+      <c r="J466" s="76"/>
+      <c r="K466" s="75"/>
       <c r="L466" s="62"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="B467" s="6"/>
-      <c r="C467" s="68"/>
-      <c r="D467" s="69"/>
+      <c r="C467" s="74"/>
+      <c r="D467" s="75"/>
       <c r="I467" s="6"/>
-      <c r="J467" s="70"/>
-      <c r="K467" s="69"/>
+      <c r="J467" s="76"/>
+      <c r="K467" s="75"/>
       <c r="L467" s="62"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="B468" s="6"/>
-      <c r="C468" s="68"/>
-      <c r="D468" s="69"/>
+      <c r="C468" s="74"/>
+      <c r="D468" s="75"/>
       <c r="I468" s="6"/>
-      <c r="J468" s="70"/>
-      <c r="K468" s="69"/>
+      <c r="J468" s="76"/>
+      <c r="K468" s="75"/>
       <c r="L468" s="62"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="B469" s="6"/>
-      <c r="C469" s="68"/>
-      <c r="D469" s="69"/>
+      <c r="C469" s="74"/>
+      <c r="D469" s="75"/>
       <c r="I469" s="6"/>
-      <c r="J469" s="70"/>
-      <c r="K469" s="69"/>
+      <c r="J469" s="76"/>
+      <c r="K469" s="75"/>
       <c r="L469" s="62"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="B470" s="6"/>
-      <c r="C470" s="68"/>
-      <c r="D470" s="69"/>
+      <c r="C470" s="74"/>
+      <c r="D470" s="75"/>
       <c r="I470" s="6"/>
-      <c r="J470" s="70"/>
-      <c r="K470" s="69"/>
+      <c r="J470" s="76"/>
+      <c r="K470" s="75"/>
       <c r="L470" s="62"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="B471" s="6"/>
-      <c r="C471" s="68"/>
-      <c r="D471" s="69"/>
+      <c r="C471" s="74"/>
+      <c r="D471" s="75"/>
       <c r="I471" s="6"/>
-      <c r="J471" s="70"/>
-      <c r="K471" s="69"/>
+      <c r="J471" s="76"/>
+      <c r="K471" s="75"/>
       <c r="L471" s="62"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="B472" s="6"/>
-      <c r="C472" s="68"/>
-      <c r="D472" s="69"/>
+      <c r="C472" s="74"/>
+      <c r="D472" s="75"/>
       <c r="I472" s="6"/>
-      <c r="J472" s="70"/>
-      <c r="K472" s="69"/>
+      <c r="J472" s="76"/>
+      <c r="K472" s="75"/>
       <c r="L472" s="62"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="B473" s="6"/>
-      <c r="C473" s="68"/>
-      <c r="D473" s="69"/>
+      <c r="C473" s="74"/>
+      <c r="D473" s="75"/>
       <c r="I473" s="6"/>
-      <c r="J473" s="70"/>
-      <c r="K473" s="69"/>
+      <c r="J473" s="76"/>
+      <c r="K473" s="75"/>
       <c r="L473" s="62"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="B474" s="6"/>
-      <c r="C474" s="68"/>
-      <c r="D474" s="69"/>
+      <c r="C474" s="74"/>
+      <c r="D474" s="75"/>
       <c r="I474" s="6"/>
-      <c r="J474" s="70"/>
-      <c r="K474" s="69"/>
+      <c r="J474" s="76"/>
+      <c r="K474" s="75"/>
       <c r="L474" s="62"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="B475" s="6"/>
-      <c r="C475" s="68"/>
-      <c r="D475" s="69"/>
+      <c r="C475" s="74"/>
+      <c r="D475" s="75"/>
       <c r="I475" s="6"/>
-      <c r="J475" s="70"/>
-      <c r="K475" s="69"/>
+      <c r="J475" s="76"/>
+      <c r="K475" s="75"/>
       <c r="L475" s="62"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="B476" s="6"/>
-      <c r="C476" s="68"/>
-      <c r="D476" s="69"/>
+      <c r="C476" s="74"/>
+      <c r="D476" s="75"/>
       <c r="I476" s="6"/>
-      <c r="J476" s="70"/>
-      <c r="K476" s="69"/>
+      <c r="J476" s="76"/>
+      <c r="K476" s="75"/>
       <c r="L476" s="62"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="B477" s="6"/>
-      <c r="C477" s="68"/>
-      <c r="D477" s="69"/>
+      <c r="C477" s="74"/>
+      <c r="D477" s="75"/>
       <c r="I477" s="6"/>
-      <c r="J477" s="70"/>
-      <c r="K477" s="69"/>
+      <c r="J477" s="76"/>
+      <c r="K477" s="75"/>
       <c r="L477" s="62"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="B478" s="6"/>
-      <c r="C478" s="68"/>
-      <c r="D478" s="69"/>
+      <c r="C478" s="74"/>
+      <c r="D478" s="75"/>
       <c r="I478" s="6"/>
-      <c r="J478" s="70"/>
-      <c r="K478" s="69"/>
+      <c r="J478" s="76"/>
+      <c r="K478" s="75"/>
       <c r="L478" s="62"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="B479" s="6"/>
-      <c r="C479" s="68"/>
-      <c r="D479" s="69"/>
+      <c r="C479" s="74"/>
+      <c r="D479" s="75"/>
       <c r="I479" s="6"/>
-      <c r="J479" s="70"/>
-      <c r="K479" s="69"/>
+      <c r="J479" s="76"/>
+      <c r="K479" s="75"/>
       <c r="L479" s="62"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="B480" s="6"/>
-      <c r="C480" s="68"/>
-      <c r="D480" s="69"/>
+      <c r="C480" s="74"/>
+      <c r="D480" s="75"/>
       <c r="I480" s="6"/>
-      <c r="J480" s="70"/>
-      <c r="K480" s="69"/>
+      <c r="J480" s="76"/>
+      <c r="K480" s="75"/>
       <c r="L480" s="62"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="B481" s="6"/>
-      <c r="C481" s="68"/>
-      <c r="D481" s="69"/>
+      <c r="C481" s="74"/>
+      <c r="D481" s="75"/>
       <c r="I481" s="6"/>
-      <c r="J481" s="70"/>
-      <c r="K481" s="69"/>
+      <c r="J481" s="76"/>
+      <c r="K481" s="75"/>
       <c r="L481" s="62"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="B482" s="6"/>
-      <c r="C482" s="68"/>
-      <c r="D482" s="69"/>
+      <c r="C482" s="74"/>
+      <c r="D482" s="75"/>
       <c r="I482" s="6"/>
-      <c r="J482" s="70"/>
-      <c r="K482" s="69"/>
+      <c r="J482" s="76"/>
+      <c r="K482" s="75"/>
       <c r="L482" s="62"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="B483" s="6"/>
-      <c r="C483" s="68"/>
-      <c r="D483" s="69"/>
+      <c r="C483" s="74"/>
+      <c r="D483" s="75"/>
       <c r="I483" s="6"/>
-      <c r="J483" s="70"/>
-      <c r="K483" s="69"/>
+      <c r="J483" s="76"/>
+      <c r="K483" s="75"/>
       <c r="L483" s="62"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="B484" s="6"/>
-      <c r="C484" s="68"/>
-      <c r="D484" s="69"/>
+      <c r="C484" s="74"/>
+      <c r="D484" s="75"/>
       <c r="I484" s="6"/>
-      <c r="J484" s="70"/>
-      <c r="K484" s="69"/>
+      <c r="J484" s="76"/>
+      <c r="K484" s="75"/>
       <c r="L484" s="62"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="B485" s="6"/>
-      <c r="C485" s="68"/>
-      <c r="D485" s="69"/>
+      <c r="C485" s="74"/>
+      <c r="D485" s="75"/>
       <c r="I485" s="6"/>
-      <c r="J485" s="70"/>
-      <c r="K485" s="69"/>
+      <c r="J485" s="76"/>
+      <c r="K485" s="75"/>
       <c r="L485" s="62"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="B486" s="6"/>
-      <c r="C486" s="68"/>
-      <c r="D486" s="69"/>
+      <c r="C486" s="74"/>
+      <c r="D486" s="75"/>
       <c r="I486" s="6"/>
-      <c r="J486" s="70"/>
-      <c r="K486" s="69"/>
+      <c r="J486" s="76"/>
+      <c r="K486" s="75"/>
       <c r="L486" s="62"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="B487" s="6"/>
-      <c r="C487" s="68"/>
-      <c r="D487" s="69"/>
+      <c r="C487" s="74"/>
+      <c r="D487" s="75"/>
       <c r="I487" s="6"/>
-      <c r="J487" s="70"/>
-      <c r="K487" s="69"/>
+      <c r="J487" s="76"/>
+      <c r="K487" s="75"/>
       <c r="L487" s="62"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="B488" s="6"/>
-      <c r="C488" s="68"/>
-      <c r="D488" s="69"/>
+      <c r="C488" s="74"/>
+      <c r="D488" s="75"/>
       <c r="I488" s="6"/>
-      <c r="J488" s="70"/>
-      <c r="K488" s="69"/>
+      <c r="J488" s="76"/>
+      <c r="K488" s="75"/>
       <c r="L488" s="62"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="B489" s="6"/>
-      <c r="C489" s="68"/>
-      <c r="D489" s="69"/>
+      <c r="C489" s="74"/>
+      <c r="D489" s="75"/>
       <c r="I489" s="6"/>
-      <c r="J489" s="70"/>
-      <c r="K489" s="69"/>
+      <c r="J489" s="76"/>
+      <c r="K489" s="75"/>
       <c r="L489" s="62"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="B490" s="6"/>
-      <c r="C490" s="68"/>
-      <c r="D490" s="69"/>
+      <c r="C490" s="74"/>
+      <c r="D490" s="75"/>
       <c r="I490" s="6"/>
-      <c r="J490" s="70"/>
-      <c r="K490" s="69"/>
+      <c r="J490" s="76"/>
+      <c r="K490" s="75"/>
       <c r="L490" s="62"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="B491" s="6"/>
-      <c r="C491" s="68"/>
-      <c r="D491" s="69"/>
+      <c r="C491" s="74"/>
+      <c r="D491" s="75"/>
       <c r="I491" s="6"/>
-      <c r="J491" s="70"/>
-      <c r="K491" s="69"/>
+      <c r="J491" s="76"/>
+      <c r="K491" s="75"/>
       <c r="L491" s="62"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="B492" s="6"/>
-      <c r="C492" s="68"/>
-      <c r="D492" s="69"/>
+      <c r="C492" s="74"/>
+      <c r="D492" s="75"/>
       <c r="I492" s="6"/>
-      <c r="J492" s="70"/>
-      <c r="K492" s="69"/>
+      <c r="J492" s="76"/>
+      <c r="K492" s="75"/>
       <c r="L492" s="62"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="B493" s="6"/>
-      <c r="C493" s="68"/>
-      <c r="D493" s="69"/>
+      <c r="C493" s="74"/>
+      <c r="D493" s="75"/>
       <c r="I493" s="6"/>
-      <c r="J493" s="70"/>
-      <c r="K493" s="69"/>
+      <c r="J493" s="76"/>
+      <c r="K493" s="75"/>
       <c r="L493" s="62"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="B494" s="6"/>
-      <c r="C494" s="68"/>
-      <c r="D494" s="69"/>
+      <c r="C494" s="74"/>
+      <c r="D494" s="75"/>
       <c r="I494" s="6"/>
-      <c r="J494" s="70"/>
-      <c r="K494" s="69"/>
+      <c r="J494" s="76"/>
+      <c r="K494" s="75"/>
       <c r="L494" s="62"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="B495" s="6"/>
-      <c r="C495" s="68"/>
-      <c r="D495" s="69"/>
+      <c r="C495" s="74"/>
+      <c r="D495" s="75"/>
       <c r="I495" s="6"/>
-      <c r="J495" s="70"/>
-      <c r="K495" s="69"/>
+      <c r="J495" s="76"/>
+      <c r="K495" s="75"/>
       <c r="L495" s="62"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="B496" s="6"/>
-      <c r="C496" s="68"/>
-      <c r="D496" s="69"/>
+      <c r="C496" s="74"/>
+      <c r="D496" s="75"/>
       <c r="I496" s="6"/>
-      <c r="J496" s="70"/>
-      <c r="K496" s="69"/>
+      <c r="J496" s="76"/>
+      <c r="K496" s="75"/>
       <c r="L496" s="62"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="B497" s="6"/>
-      <c r="C497" s="68"/>
-      <c r="D497" s="69"/>
+      <c r="C497" s="74"/>
+      <c r="D497" s="75"/>
       <c r="I497" s="6"/>
-      <c r="J497" s="70"/>
-      <c r="K497" s="69"/>
+      <c r="J497" s="76"/>
+      <c r="K497" s="75"/>
       <c r="L497" s="62"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="B498" s="6"/>
-      <c r="C498" s="68"/>
-      <c r="D498" s="69"/>
+      <c r="C498" s="74"/>
+      <c r="D498" s="75"/>
       <c r="I498" s="6"/>
-      <c r="J498" s="70"/>
-      <c r="K498" s="69"/>
+      <c r="J498" s="76"/>
+      <c r="K498" s="75"/>
       <c r="L498" s="62"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="B499" s="6"/>
-      <c r="C499" s="68"/>
-      <c r="D499" s="69"/>
+      <c r="C499" s="74"/>
+      <c r="D499" s="75"/>
       <c r="I499" s="6"/>
-      <c r="J499" s="70"/>
-      <c r="K499" s="69"/>
+      <c r="J499" s="76"/>
+      <c r="K499" s="75"/>
       <c r="L499" s="62"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="B500" s="6"/>
-      <c r="C500" s="68"/>
-      <c r="D500" s="69"/>
+      <c r="C500" s="74"/>
+      <c r="D500" s="75"/>
       <c r="I500" s="6"/>
-      <c r="J500" s="70"/>
-      <c r="K500" s="69"/>
+      <c r="J500" s="76"/>
+      <c r="K500" s="75"/>
       <c r="L500" s="62"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="B501" s="6"/>
-      <c r="C501" s="68"/>
-      <c r="D501" s="69"/>
+      <c r="C501" s="74"/>
+      <c r="D501" s="75"/>
       <c r="I501" s="6"/>
-      <c r="J501" s="70"/>
-      <c r="K501" s="69"/>
+      <c r="J501" s="76"/>
+      <c r="K501" s="75"/>
       <c r="L501" s="62"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="B502" s="6"/>
-      <c r="C502" s="68"/>
-      <c r="D502" s="69"/>
+      <c r="C502" s="74"/>
+      <c r="D502" s="75"/>
       <c r="I502" s="6"/>
-      <c r="J502" s="70"/>
-      <c r="K502" s="69"/>
+      <c r="J502" s="76"/>
+      <c r="K502" s="75"/>
       <c r="L502" s="62"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="B503" s="6"/>
-      <c r="C503" s="68"/>
-      <c r="D503" s="69"/>
+      <c r="C503" s="74"/>
+      <c r="D503" s="75"/>
       <c r="I503" s="6"/>
-      <c r="J503" s="70"/>
-      <c r="K503" s="69"/>
+      <c r="J503" s="76"/>
+      <c r="K503" s="75"/>
       <c r="L503" s="62"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="B504" s="6"/>
-      <c r="C504" s="68"/>
-      <c r="D504" s="69"/>
+      <c r="C504" s="74"/>
+      <c r="D504" s="75"/>
       <c r="I504" s="6"/>
-      <c r="J504" s="70"/>
-      <c r="K504" s="69"/>
+      <c r="J504" s="76"/>
+      <c r="K504" s="75"/>
       <c r="L504" s="62"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="B505" s="6"/>
-      <c r="C505" s="68"/>
-      <c r="D505" s="69"/>
+      <c r="C505" s="74"/>
+      <c r="D505" s="75"/>
       <c r="I505" s="6"/>
-      <c r="J505" s="70"/>
-      <c r="K505" s="69"/>
+      <c r="J505" s="76"/>
+      <c r="K505" s="75"/>
       <c r="L505" s="62"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="B506" s="6"/>
-      <c r="C506" s="68"/>
-      <c r="D506" s="69"/>
+      <c r="C506" s="74"/>
+      <c r="D506" s="75"/>
       <c r="I506" s="6"/>
-      <c r="J506" s="70"/>
-      <c r="K506" s="69"/>
+      <c r="J506" s="76"/>
+      <c r="K506" s="75"/>
       <c r="L506" s="62"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="B507" s="6"/>
-      <c r="C507" s="68"/>
-      <c r="D507" s="69"/>
+      <c r="C507" s="74"/>
+      <c r="D507" s="75"/>
       <c r="I507" s="6"/>
-      <c r="J507" s="70"/>
-      <c r="K507" s="69"/>
+      <c r="J507" s="76"/>
+      <c r="K507" s="75"/>
       <c r="L507" s="62"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="B508" s="6"/>
-      <c r="C508" s="68"/>
-      <c r="D508" s="69"/>
+      <c r="C508" s="74"/>
+      <c r="D508" s="75"/>
       <c r="I508" s="6"/>
-      <c r="J508" s="70"/>
-      <c r="K508" s="69"/>
+      <c r="J508" s="76"/>
+      <c r="K508" s="75"/>
       <c r="L508" s="62"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="B509" s="6"/>
-      <c r="C509" s="68"/>
-      <c r="D509" s="69"/>
+      <c r="C509" s="74"/>
+      <c r="D509" s="75"/>
       <c r="I509" s="6"/>
-      <c r="J509" s="70"/>
-      <c r="K509" s="69"/>
+      <c r="J509" s="76"/>
+      <c r="K509" s="75"/>
       <c r="L509" s="62"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="B510" s="6"/>
-      <c r="C510" s="68"/>
-      <c r="D510" s="69"/>
+      <c r="C510" s="74"/>
+      <c r="D510" s="75"/>
       <c r="I510" s="6"/>
-      <c r="J510" s="70"/>
-      <c r="K510" s="69"/>
+      <c r="J510" s="76"/>
+      <c r="K510" s="75"/>
       <c r="L510" s="62"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="B511" s="6"/>
-      <c r="C511" s="68"/>
-      <c r="D511" s="69"/>
+      <c r="C511" s="74"/>
+      <c r="D511" s="75"/>
       <c r="I511" s="6"/>
-      <c r="J511" s="70"/>
-      <c r="K511" s="69"/>
+      <c r="J511" s="76"/>
+      <c r="K511" s="75"/>
       <c r="L511" s="62"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="B512" s="6"/>
-      <c r="C512" s="68"/>
-      <c r="D512" s="69"/>
+      <c r="C512" s="74"/>
+      <c r="D512" s="75"/>
       <c r="I512" s="6"/>
-      <c r="J512" s="70"/>
-      <c r="K512" s="69"/>
+      <c r="J512" s="76"/>
+      <c r="K512" s="75"/>
       <c r="L512" s="62"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="B513" s="6"/>
-      <c r="C513" s="68"/>
-      <c r="D513" s="69"/>
+      <c r="C513" s="74"/>
+      <c r="D513" s="75"/>
       <c r="I513" s="6"/>
-      <c r="J513" s="70"/>
-      <c r="K513" s="69"/>
+      <c r="J513" s="76"/>
+      <c r="K513" s="75"/>
       <c r="L513" s="62"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="B514" s="6"/>
-      <c r="C514" s="68"/>
-      <c r="D514" s="69"/>
+      <c r="C514" s="74"/>
+      <c r="D514" s="75"/>
       <c r="I514" s="6"/>
-      <c r="J514" s="70"/>
-      <c r="K514" s="69"/>
+      <c r="J514" s="76"/>
+      <c r="K514" s="75"/>
       <c r="L514" s="62"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="B515" s="6"/>
-      <c r="C515" s="68"/>
-      <c r="D515" s="69"/>
+      <c r="C515" s="74"/>
+      <c r="D515" s="75"/>
       <c r="I515" s="6"/>
-      <c r="J515" s="70"/>
-      <c r="K515" s="69"/>
+      <c r="J515" s="76"/>
+      <c r="K515" s="75"/>
       <c r="L515" s="62"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="B516" s="6"/>
-      <c r="C516" s="68"/>
-      <c r="D516" s="69"/>
+      <c r="C516" s="74"/>
+      <c r="D516" s="75"/>
       <c r="I516" s="6"/>
-      <c r="J516" s="70"/>
-      <c r="K516" s="69"/>
+      <c r="J516" s="76"/>
+      <c r="K516" s="75"/>
       <c r="L516" s="62"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="B517" s="6"/>
-      <c r="C517" s="68"/>
-      <c r="D517" s="69"/>
+      <c r="C517" s="74"/>
+      <c r="D517" s="75"/>
       <c r="I517" s="6"/>
-      <c r="J517" s="70"/>
-      <c r="K517" s="69"/>
+      <c r="J517" s="76"/>
+      <c r="K517" s="75"/>
       <c r="L517" s="62"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="B518" s="6"/>
-      <c r="C518" s="68"/>
-      <c r="D518" s="69"/>
+      <c r="C518" s="74"/>
+      <c r="D518" s="75"/>
       <c r="I518" s="6"/>
-      <c r="J518" s="70"/>
-      <c r="K518" s="69"/>
+      <c r="J518" s="76"/>
+      <c r="K518" s="75"/>
       <c r="L518" s="62"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="B519" s="6"/>
-      <c r="C519" s="68"/>
-      <c r="D519" s="69"/>
+      <c r="C519" s="74"/>
+      <c r="D519" s="75"/>
       <c r="I519" s="6"/>
-      <c r="J519" s="70"/>
-      <c r="K519" s="69"/>
+      <c r="J519" s="76"/>
+      <c r="K519" s="75"/>
       <c r="L519" s="62"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="B520" s="6"/>
-      <c r="C520" s="68"/>
-      <c r="D520" s="69"/>
+      <c r="C520" s="74"/>
+      <c r="D520" s="75"/>
       <c r="I520" s="6"/>
-      <c r="J520" s="70"/>
-      <c r="K520" s="69"/>
+      <c r="J520" s="76"/>
+      <c r="K520" s="75"/>
       <c r="L520" s="62"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="B521" s="6"/>
-      <c r="C521" s="68"/>
-      <c r="D521" s="69"/>
+      <c r="C521" s="74"/>
+      <c r="D521" s="75"/>
       <c r="I521" s="6"/>
-      <c r="J521" s="70"/>
-      <c r="K521" s="69"/>
+      <c r="J521" s="76"/>
+      <c r="K521" s="75"/>
       <c r="L521" s="62"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="B522" s="6"/>
-      <c r="C522" s="68"/>
-      <c r="D522" s="69"/>
+      <c r="C522" s="74"/>
+      <c r="D522" s="75"/>
       <c r="I522" s="6"/>
-      <c r="J522" s="70"/>
-      <c r="K522" s="69"/>
+      <c r="J522" s="76"/>
+      <c r="K522" s="75"/>
       <c r="L522" s="62"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="B523" s="6"/>
-      <c r="C523" s="68"/>
-      <c r="D523" s="69"/>
+      <c r="C523" s="74"/>
+      <c r="D523" s="75"/>
       <c r="I523" s="6"/>
-      <c r="J523" s="70"/>
-      <c r="K523" s="69"/>
+      <c r="J523" s="76"/>
+      <c r="K523" s="75"/>
       <c r="L523" s="62"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="B524" s="6"/>
-      <c r="C524" s="68"/>
-      <c r="D524" s="69"/>
+      <c r="C524" s="74"/>
+      <c r="D524" s="75"/>
       <c r="I524" s="6"/>
-      <c r="J524" s="70"/>
-      <c r="K524" s="69"/>
+      <c r="J524" s="76"/>
+      <c r="K524" s="75"/>
       <c r="L524" s="62"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="B525" s="6"/>
-      <c r="C525" s="68"/>
-      <c r="D525" s="69"/>
+      <c r="C525" s="74"/>
+      <c r="D525" s="75"/>
       <c r="I525" s="6"/>
-      <c r="J525" s="70"/>
-      <c r="K525" s="69"/>
+      <c r="J525" s="76"/>
+      <c r="K525" s="75"/>
       <c r="L525" s="62"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="B526" s="6"/>
-      <c r="C526" s="68"/>
-      <c r="D526" s="69"/>
+      <c r="C526" s="74"/>
+      <c r="D526" s="75"/>
       <c r="I526" s="6"/>
-      <c r="J526" s="70"/>
-      <c r="K526" s="69"/>
+      <c r="J526" s="76"/>
+      <c r="K526" s="75"/>
       <c r="L526" s="62"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="B527" s="6"/>
-      <c r="C527" s="68"/>
-      <c r="D527" s="69"/>
+      <c r="C527" s="74"/>
+      <c r="D527" s="75"/>
       <c r="I527" s="6"/>
-      <c r="J527" s="70"/>
-      <c r="K527" s="69"/>
+      <c r="J527" s="76"/>
+      <c r="K527" s="75"/>
       <c r="L527" s="62"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="B528" s="6"/>
-      <c r="C528" s="68"/>
-      <c r="D528" s="69"/>
+      <c r="C528" s="74"/>
+      <c r="D528" s="75"/>
       <c r="I528" s="6"/>
-      <c r="J528" s="70"/>
-      <c r="K528" s="69"/>
+      <c r="J528" s="76"/>
+      <c r="K528" s="75"/>
       <c r="L528" s="62"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="B529" s="6"/>
-      <c r="C529" s="68"/>
-      <c r="D529" s="69"/>
+      <c r="C529" s="74"/>
+      <c r="D529" s="75"/>
       <c r="I529" s="6"/>
-      <c r="J529" s="70"/>
-      <c r="K529" s="69"/>
+      <c r="J529" s="76"/>
+      <c r="K529" s="75"/>
       <c r="L529" s="62"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="B530" s="6"/>
-      <c r="C530" s="68"/>
-      <c r="D530" s="69"/>
+      <c r="C530" s="74"/>
+      <c r="D530" s="75"/>
       <c r="I530" s="6"/>
-      <c r="J530" s="70"/>
-      <c r="K530" s="69"/>
+      <c r="J530" s="76"/>
+      <c r="K530" s="75"/>
       <c r="L530" s="62"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="B531" s="6"/>
-      <c r="C531" s="68"/>
-      <c r="D531" s="69"/>
+      <c r="C531" s="74"/>
+      <c r="D531" s="75"/>
       <c r="I531" s="6"/>
-      <c r="J531" s="70"/>
-      <c r="K531" s="69"/>
+      <c r="J531" s="76"/>
+      <c r="K531" s="75"/>
       <c r="L531" s="62"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="B532" s="6"/>
-      <c r="C532" s="68"/>
-      <c r="D532" s="69"/>
+      <c r="C532" s="74"/>
+      <c r="D532" s="75"/>
       <c r="I532" s="6"/>
-      <c r="J532" s="70"/>
-      <c r="K532" s="69"/>
+      <c r="J532" s="76"/>
+      <c r="K532" s="75"/>
       <c r="L532" s="62"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="B533" s="6"/>
-      <c r="C533" s="68"/>
-      <c r="D533" s="69"/>
+      <c r="C533" s="74"/>
+      <c r="D533" s="75"/>
       <c r="I533" s="6"/>
-      <c r="J533" s="70"/>
-      <c r="K533" s="69"/>
+      <c r="J533" s="76"/>
+      <c r="K533" s="75"/>
       <c r="L533" s="62"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="B534" s="6"/>
-      <c r="C534" s="68"/>
-      <c r="D534" s="69"/>
+      <c r="C534" s="74"/>
+      <c r="D534" s="75"/>
       <c r="I534" s="6"/>
-      <c r="J534" s="70"/>
-      <c r="K534" s="69"/>
+      <c r="J534" s="76"/>
+      <c r="K534" s="75"/>
       <c r="L534" s="62"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="B535" s="6"/>
-      <c r="C535" s="68"/>
-      <c r="D535" s="69"/>
+      <c r="C535" s="74"/>
+      <c r="D535" s="75"/>
       <c r="I535" s="6"/>
-      <c r="J535" s="70"/>
-      <c r="K535" s="69"/>
+      <c r="J535" s="76"/>
+      <c r="K535" s="75"/>
       <c r="L535" s="62"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="B536" s="6"/>
-      <c r="C536" s="68"/>
-      <c r="D536" s="69"/>
+      <c r="C536" s="74"/>
+      <c r="D536" s="75"/>
       <c r="I536" s="6"/>
-      <c r="J536" s="70"/>
-      <c r="K536" s="69"/>
+      <c r="J536" s="76"/>
+      <c r="K536" s="75"/>
       <c r="L536" s="62"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
-      <c r="B537" s="62"/>
-      <c r="C537" s="62"/>
-      <c r="D537" s="62"/>
-      <c r="I537" s="62"/>
-      <c r="J537" s="62"/>
-      <c r="K537" s="62"/>
+    <row r="537" ht="12.75" customHeight="1">
+      <c r="B537" s="6"/>
+      <c r="C537" s="74"/>
+      <c r="D537" s="75"/>
+      <c r="I537" s="6"/>
+      <c r="J537" s="76"/>
+      <c r="K537" s="75"/>
       <c r="L537" s="62"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
@@ -20352,7 +20416,15 @@
       <c r="K657" s="62"/>
       <c r="L657" s="62"/>
     </row>
-    <row r="658" ht="12.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="B658" s="62"/>
+      <c r="C658" s="62"/>
+      <c r="D658" s="62"/>
+      <c r="I658" s="62"/>
+      <c r="J658" s="62"/>
+      <c r="K658" s="62"/>
+      <c r="L658" s="62"/>
+    </row>
     <row r="659" ht="12.75" customHeight="1"/>
     <row r="660" ht="12.75" customHeight="1"/>
     <row r="661" ht="12.75" customHeight="1"/>
@@ -20695,6 +20767,7 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="84">
     <mergeCell ref="A287:J287"/>
@@ -20719,12 +20792,12 @@
     <mergeCell ref="A394:J394"/>
     <mergeCell ref="A396:K396"/>
     <mergeCell ref="A433:K433"/>
-    <mergeCell ref="A437:J437"/>
-    <mergeCell ref="A439:K439"/>
-    <mergeCell ref="A443:J443"/>
-    <mergeCell ref="A445:K445"/>
-    <mergeCell ref="A453:J453"/>
-    <mergeCell ref="A455:K455"/>
+    <mergeCell ref="A438:J438"/>
+    <mergeCell ref="A440:K440"/>
+    <mergeCell ref="A444:J444"/>
+    <mergeCell ref="A446:K446"/>
+    <mergeCell ref="A454:J454"/>
+    <mergeCell ref="A456:K456"/>
     <mergeCell ref="A406:J406"/>
     <mergeCell ref="A408:K408"/>
     <mergeCell ref="A420:J420"/>
